--- a/main/ig/StructureDefinition-fr-lm-device-use.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-device-use.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-device-use.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-device-use.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-device-use.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-device-use.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-device-use.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-device-use.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-device-use.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-device-use.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-device-use.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-device-use.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-device-use.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-device-use.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-device-use.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-device-use.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -426,6 +426,9 @@
   </si>
   <si>
     <t>Statut</t>
+  </si>
+  <si>
+    <t>required</t>
   </si>
   <si>
     <t>Valeur issue du http://hl7.org/fhir/ValueSet/device-statement-status</t>
@@ -590,10 +593,7 @@
 </t>
   </si>
   <si>
-    <t>localisation anatomique</t>
-  </si>
-  <si>
-    <t>SNOMED CT (2.16.840.1.113883.6.96)</t>
+    <t>localisation anatomique. Le code de la localisation doit être issu de SNOMED CT (2.16.840.1.113883.6.96)</t>
   </si>
   <si>
     <t>fr-lm-device-use.reason[x]</t>
@@ -2626,13 +2626,13 @@
         <v>73</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
@@ -2650,7 +2650,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
@@ -2667,10 +2667,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2696,10 +2696,10 @@
         <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2750,7 +2750,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2767,10 +2767,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2796,10 +2796,10 @@
         <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2850,7 +2850,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2867,10 +2867,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2893,13 +2893,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2950,7 +2950,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -2962,15 +2962,15 @@
         <v>73</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2993,13 +2993,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3050,7 +3050,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -3067,14 +3067,14 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -3093,16 +3093,16 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3140,19 +3140,19 @@
         <v>73</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3164,15 +3164,15 @@
         <v>73</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3195,16 +3195,16 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3254,7 +3254,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -3271,10 +3271,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3297,13 +3297,13 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3354,7 +3354,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3366,15 +3366,15 @@
         <v>73</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3400,10 +3400,10 @@
         <v>127</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3454,7 +3454,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3471,10 +3471,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3500,10 +3500,10 @@
         <v>127</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3554,7 +3554,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3571,10 +3571,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3600,10 +3600,10 @@
         <v>127</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3654,7 +3654,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3671,10 +3671,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3700,10 +3700,10 @@
         <v>103</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3754,7 +3754,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -3771,10 +3771,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3797,13 +3797,13 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3833,7 +3833,7 @@
         <v>73</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>185</v>
+        <v>73</v>
       </c>
       <c r="Z29" t="s" s="2">
         <v>73</v>
@@ -3854,7 +3854,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -3997,7 +3997,7 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>190</v>
